--- a/product_upload/packages/12/file.xlsx
+++ b/product_upload/packages/12/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -840,6 +845,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>SUPRAZOLE 200 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-FBC6B44F1AF7</t>
         </is>
       </c>
@@ -863,7 +873,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1034,6 +1044,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>SUPRAX D 400MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-DB3325339C28</t>
         </is>
       </c>
@@ -1057,7 +1072,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1228,6 +1243,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>STALORAL POLLENS INITIAL</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-FF6A33E1597F</t>
         </is>
       </c>
@@ -1251,7 +1271,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1410,6 +1430,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>STELAZINE 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-37A4FB47B3E3</t>
         </is>
       </c>
@@ -1433,7 +1458,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1592,6 +1617,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>STELAZINE 1MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-96B66486A817</t>
         </is>
       </c>
@@ -1615,7 +1645,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1772,6 +1802,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>STERILE WATER FOR INJ 500 ML</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-510319876917</t>
         </is>
       </c>
@@ -1795,7 +1830,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1952,6 +1987,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>STERILE WATER FOR IRRIG.IN ACCUMED PS.CT</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-4F61F2894B09</t>
         </is>
       </c>
@@ -1975,7 +2015,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2132,6 +2172,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>STERILE WATER FOR IRRIG.IN ACCUMED PS.CT</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-FEB578CA85E8</t>
         </is>
       </c>
@@ -2155,7 +2200,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2316,6 +2361,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>STERILE WATER FOR IRRIG.IN ACCUMED PS.CT</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-07A9F68D53BC</t>
         </is>
       </c>
@@ -2339,7 +2389,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2502,6 +2552,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>STIEPROX 1.5% SHAMPOO</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-7741CD9B949E</t>
         </is>
       </c>
@@ -2525,7 +2580,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2686,6 +2741,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>STERILE WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-397E1026A2E3</t>
         </is>
       </c>
@@ -2709,7 +2769,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2870,6 +2930,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>STERILE WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-3C44721016A0</t>
         </is>
       </c>
@@ -2893,7 +2958,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3058,6 +3123,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>STERILE WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-D5C5DA7796FC</t>
         </is>
       </c>
@@ -3081,7 +3151,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3242,6 +3312,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>STERILE WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-0D0D3F67090A</t>
         </is>
       </c>
@@ -3265,7 +3340,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3432,6 +3507,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>SMOFKABIVEN PERIPHERAL EMULSION for infusion</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-1B94D7D219BB</t>
         </is>
       </c>
@@ -3455,7 +3535,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3628,6 +3708,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>SINEMET 25-250MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-D8FFB1565C36</t>
         </is>
       </c>
@@ -3651,7 +3736,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3818,6 +3903,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>SINATEN 100000 I.U VAGINAL TAB.</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-F56D46B18515</t>
         </is>
       </c>
@@ -3841,7 +3931,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4004,6 +4094,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>SIMVAGEN 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-087D8A452049</t>
         </is>
       </c>
@@ -4027,7 +4122,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4190,6 +4285,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>SIMVAGEN 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-2194926A953F</t>
         </is>
       </c>
@@ -4213,7 +4313,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4372,6 +4472,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>SIMVAGEN 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-1BB4532F45F5</t>
         </is>
       </c>
@@ -4395,7 +4500,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4566,6 +4671,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>SIMVA 40 MG COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-70204355BDBA</t>
         </is>
       </c>
@@ -4589,7 +4699,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4760,6 +4870,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>SIMVA 20 MG COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-946F8240D797</t>
         </is>
       </c>
@@ -4783,7 +4898,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4950,6 +5065,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>SMOFKABIVEN PERIPHERAL EMULSION for infusion</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-D1AEAC9B2899</t>
         </is>
       </c>
@@ -4973,7 +5093,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5144,6 +5264,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>SMOFKABIVEN PERIPHERAL EMULSION for infusion</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-069AF76C4083</t>
         </is>
       </c>
@@ -5167,7 +5292,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5326,6 +5451,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>SNAFI 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-428311B5C8E0</t>
         </is>
       </c>
@@ -5349,7 +5479,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5516,6 +5646,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>SIMVA 10 MG COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-3B1C9F5AA8C0</t>
         </is>
       </c>
@@ -5539,7 +5674,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5702,6 +5837,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>SOD. CHLORIDE 0.45%+DEXTROSE 5% I.V INF.</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-B6F21B63CA4B</t>
         </is>
       </c>
@@ -5725,7 +5865,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5888,6 +6028,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>SIMCOR 20 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-03C6C2DB525B</t>
         </is>
       </c>
@@ -5911,7 +6056,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6066,6 +6211,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>SILVER NITRATE EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-CCE964DF257A</t>
         </is>
       </c>
@@ -6089,7 +6239,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6252,6 +6402,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>SEROQUEL 300MG F-C TABS</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-9D64F2709C30</t>
         </is>
       </c>
@@ -6275,7 +6430,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6438,6 +6593,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>SEROQUEL 25 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-2993C83D6939</t>
         </is>
       </c>
@@ -6461,7 +6621,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6632,6 +6792,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>SEROQUEL 200 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-5C069B6FC1D9</t>
         </is>
       </c>
@@ -6655,7 +6820,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6822,6 +6987,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>SEROQUEL 100 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-25D17B900906</t>
         </is>
       </c>
@@ -6845,7 +7015,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7008,6 +7178,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>SERMION TAB 5MG</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-81633A68F14A</t>
         </is>
       </c>
@@ -7031,7 +7206,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7190,6 +7365,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>SERMION 10MG TAB</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-57247642B89E</t>
         </is>
       </c>
@@ -7213,7 +7393,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7376,6 +7556,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>SERETIDE EVOHALER 25/50</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-12FB6957F217</t>
         </is>
       </c>
@@ -7399,7 +7584,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7566,6 +7751,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>SERETIDE EVOHALER</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-91CB53B48A59</t>
         </is>
       </c>
@@ -7589,7 +7779,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7756,6 +7946,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>SERETIDE EVOHALER</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-FDBBDF6E3B27</t>
         </is>
       </c>
@@ -7779,7 +7974,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7948,6 +8143,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>SERETIDE DISKUS 50\500 MCG</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-31EF954EE485</t>
         </is>
       </c>
@@ -7971,7 +8171,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8144,6 +8344,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>SERETIDE DISKUS</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-6BA2FD5290AC</t>
         </is>
       </c>
@@ -8167,7 +8372,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8332,6 +8537,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>SERETIDE DISKUS</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-032EBE19CBAF</t>
         </is>
       </c>
@@ -8355,7 +8565,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8514,6 +8724,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>SEROQUEL XL 200MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-31EA0D317EDB</t>
         </is>
       </c>
@@ -8537,7 +8752,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8704,6 +8919,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>SEROQUEL XL 300MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-86A7D4917F51</t>
         </is>
       </c>
@@ -8727,7 +8947,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8898,6 +9118,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>SEROQUEL XL 400MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-8086E84D415F</t>
         </is>
       </c>
@@ -8921,7 +9146,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9088,6 +9313,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>SEROQUEL XL 50MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-6090CFACAE86</t>
         </is>
       </c>
@@ -9111,7 +9341,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9280,6 +9510,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>SIFROL 0.7MG (EQU. 1.00MG) TAB</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-E2F2C7618BF3</t>
         </is>
       </c>
@@ -9303,7 +9538,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9472,6 +9707,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>SIFROL 0.18 MG (EQU.0.25MG) TAB</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-24532864B5CB</t>
         </is>
       </c>
@@ -9495,7 +9735,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9666,6 +9906,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>SEVIKAR 40/5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-285B9EC47B29</t>
         </is>
       </c>
@@ -9689,7 +9934,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9856,6 +10101,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>SEVIKAR 40/10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-7B26740635D9</t>
         </is>
       </c>
@@ -9879,7 +10129,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10046,6 +10296,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>SIMCOR 10 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-24146587910F</t>
         </is>
       </c>
@@ -10069,7 +10324,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10240,6 +10495,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>SEVIKAR 20/5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-A929C21C552A</t>
         </is>
       </c>
@@ -10263,7 +10523,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10434,6 +10694,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>SETRAL 50MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-A7E97C0BD5BD</t>
         </is>
       </c>
@@ -10457,7 +10722,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10628,6 +10893,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>SETRAL 50MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-F6E65C0E9391</t>
         </is>
       </c>
@@ -10651,7 +10921,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10818,6 +11088,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>SETRAL 100MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-DBCB413152D6</t>
         </is>
       </c>
@@ -10841,7 +11116,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11012,6 +11287,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>SEROXAT CR 25MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-D9CEFD7175EA</t>
         </is>
       </c>
@@ -11035,7 +11315,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11206,6 +11486,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>SEROXAT CR 12.5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-0A59C23F567A</t>
         </is>
       </c>
@@ -11229,7 +11514,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11394,6 +11679,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>SEROXAT 20MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-6F288E552E47</t>
         </is>
       </c>
@@ -11417,7 +11707,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11584,6 +11874,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>SEVIKAR 20/10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-D992A870C426</t>
         </is>
       </c>
@@ -11607,7 +11902,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11770,6 +12065,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>SODIUM CHLORIDE .9% + DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-F15ED6EBDD53</t>
         </is>
       </c>
@@ -11793,7 +12093,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11960,6 +12260,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>SODIUM CHLORIDE 0.9% &amp; GLUCOSE 5% I.V</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-68848E72B709</t>
         </is>
       </c>
@@ -11983,7 +12288,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12146,6 +12451,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>SODIUM CHLORIDE 0.45% AND GLUCOSE 5% I.V</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-B9F644043E96</t>
         </is>
       </c>
@@ -12169,7 +12479,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12340,6 +12650,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>SODIUM CHLORIDE 0.225&amp;+DEXTROSE5%I.V INF</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-F65DF1F8B66C</t>
         </is>
       </c>
@@ -12363,7 +12678,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12526,6 +12841,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>SODIUM ACETATE F.T.V.40mEq</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-64E03CAAFF28</t>
         </is>
       </c>
@@ -12549,7 +12869,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12712,6 +13032,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>SOD.CHLORIDE 0.9% FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-AEA1A73FC31D</t>
         </is>
       </c>
@@ -12735,7 +13060,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12902,6 +13227,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>SOD.CHLORIDE 0.9% FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-AE9704D1245A</t>
         </is>
       </c>
@@ -12925,7 +13255,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13088,6 +13418,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>SOD.CHLORIDE 0.9% FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-2D01B25906D4</t>
         </is>
       </c>
@@ -13111,7 +13446,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13270,6 +13605,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>SOD.CHLORIDE 0.9% FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-6033963B8662</t>
         </is>
       </c>
@@ -13293,7 +13633,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13456,6 +13796,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>SOD.CHLORIDE 0.9% FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-BA23426A6DEE</t>
         </is>
       </c>
@@ -13479,7 +13824,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13638,6 +13983,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>0.9% w/v SODIUM CHLORIDE for irrigation</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-E9FC15711D3C</t>
         </is>
       </c>
@@ -13661,7 +14011,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13824,6 +14174,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>SOD.CHLORIDE 0.9% FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-61CA40C90302</t>
         </is>
       </c>
@@ -13847,7 +14202,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14014,6 +14369,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>LACTATED RINGERS INJECTION USP 500 ML</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-E8A6ED7C8D24</t>
         </is>
       </c>
@@ -14037,7 +14397,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14208,6 +14568,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>CLIMEN TABLETS</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-6C7260D39AEE</t>
         </is>
       </c>
@@ -14231,7 +14596,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14402,6 +14767,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>CLENIL FORTE 250MCG PUFF METERED INHALER</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-4EB3678D0FD8</t>
         </is>
       </c>
@@ -14425,7 +14795,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14596,6 +14966,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>CLAVODAR 625GM FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-5A3CBA87A288</t>
         </is>
       </c>
@@ -14619,7 +14994,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14774,6 +15149,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>CLAVODAR 457MG/5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-8C90FF3A0A27</t>
         </is>
       </c>
@@ -14797,7 +15177,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14968,6 +15348,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>CLAVODAR 1GM F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-8BF736FD1D64</t>
         </is>
       </c>
@@ -14991,7 +15376,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15158,6 +15543,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>CLARIXIN 500 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-AE4C84B6A780</t>
         </is>
       </c>
@@ -15181,7 +15571,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15344,6 +15734,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>CLARIVA 250 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-CC28EB34240E</t>
         </is>
       </c>
@@ -15367,7 +15762,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15526,6 +15921,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>CLARITT XL 500MG EXTENDED RELEASE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-EF1A7A2859A0</t>
         </is>
       </c>
@@ -15549,7 +15949,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15720,6 +16120,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>CLINDASOL 10MG-ML Solution</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-1AD5840B618E</t>
         </is>
       </c>
@@ -15743,7 +16148,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15902,6 +16307,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>CLINIMYCIN-T</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-706B52B24AEE</t>
         </is>
       </c>
@@ -15925,7 +16335,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16088,6 +16498,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>CLINIMYCIN-T</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-852E177A31A0</t>
         </is>
       </c>
@@ -16111,7 +16526,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16274,6 +16689,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>CLIOCORT</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-805B4A61029E</t>
         </is>
       </c>
@@ -16297,7 +16717,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16460,6 +16880,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>CLOPIXOL TABS 25MG</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-EC1C89295705</t>
         </is>
       </c>
@@ -16483,7 +16908,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16646,6 +17071,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>CLOPIXOL TABS 10MG</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-523EFA19B97E</t>
         </is>
       </c>
@@ -16669,7 +17099,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16828,6 +17258,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>CLARITT XL 500 MG EXTENDED RELEASE TAB.</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-41735D5F25D0</t>
         </is>
       </c>
@@ -16851,7 +17286,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17010,6 +17445,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>CLOFAST 1% GEL</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-9830915E790F</t>
         </is>
       </c>
@@ -17033,7 +17473,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17200,6 +17640,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>CLODERM 0.05% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-114D15D662C4</t>
         </is>
       </c>
@@ -17223,7 +17668,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17386,6 +17831,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>CLODERM 0.05% CREAM</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-BE8BE9149B27</t>
         </is>
       </c>
@@ -17409,7 +17859,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17572,6 +18022,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>CLOBESON</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-539565360EB8</t>
         </is>
       </c>
@@ -17595,7 +18050,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17750,6 +18205,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>CLOBEDERM</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-391FD6CD0717</t>
         </is>
       </c>
@@ -17773,7 +18233,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17936,6 +18396,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>CLORACEF 250MG/5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-02768099F7F4</t>
         </is>
       </c>
@@ -17959,7 +18424,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18126,6 +18591,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>CLARITT 500 MG FILM COATED TAB</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-3560518097A4</t>
         </is>
       </c>
@@ -18149,7 +18619,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18308,6 +18778,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>CLARITT 250 MG - 5 ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-1262E7E57027</t>
         </is>
       </c>
@@ -18331,7 +18806,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18494,6 +18969,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>CITANEST 3% DENTAL OCTAPRESSIN CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-39B1C77F646B</t>
         </is>
       </c>
@@ -18517,7 +18997,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18684,6 +19164,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>CITALOPRAM HEXAL 40MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-55E085EC13CA</t>
         </is>
       </c>
@@ -18707,7 +19192,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18870,6 +19355,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>CITALOPRAM HEXAL 20MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-90376E4C55B6</t>
         </is>
       </c>
@@ -18893,7 +19383,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19056,6 +19546,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>CITALOGEN 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-3FA0093E15B1</t>
         </is>
       </c>
@@ -19079,7 +19574,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19246,6 +19741,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>CITALOGEN 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-E140E76789F2</t>
         </is>
       </c>
@@ -19269,7 +19769,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19431,6 +19931,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>CITRIN 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-CFDFC3B5F973</t>
         </is>
@@ -19447,7 +19952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19493,100 +19998,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19618,7 +20128,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19633,92 +20143,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-22440</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>279.75</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>25</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19750,7 +20265,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19765,92 +20280,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-27418</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>223.52</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>26</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19882,7 +20402,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19897,92 +20417,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-70129</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>387.33</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>27</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20014,7 +20539,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20029,92 +20554,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-13759</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>203.4</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>28</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20146,7 +20676,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20161,92 +20691,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-23197</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>273.57</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>29</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20278,7 +20813,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20293,92 +20828,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-33253</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>186.69</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>30</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20410,7 +20950,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20425,92 +20965,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-25393</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>106.25</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>31</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20542,7 +21087,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20557,92 +21102,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-28709</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>44.52</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>32</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20674,7 +21224,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20689,92 +21239,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-28057</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>134.35</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>33</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20806,7 +21361,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20821,92 +21376,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-30435</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>142.46</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>34</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20938,7 +21498,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20953,92 +21513,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-93871</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>104.55</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>35</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21070,7 +21635,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21085,92 +21650,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-54871</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>121.11</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>36</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21187,7 +21757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21293,6 +21863,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21328,7 +21908,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21393,6 +21973,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-BEAE6FDB35E0</t>
         </is>
@@ -21429,7 +22019,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21494,6 +22084,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-F4E9C3C5015C</t>
         </is>
@@ -21530,7 +22130,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21595,6 +22195,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-10F31E1B83B8</t>
         </is>
@@ -21631,7 +22241,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21696,6 +22306,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-3456071ACD86</t>
         </is>
@@ -21732,7 +22352,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21797,6 +22417,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-58AE8919296C</t>
         </is>
@@ -21833,7 +22463,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21898,6 +22528,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-30257D494980</t>
         </is>
@@ -21934,7 +22574,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21999,6 +22639,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-7A81459AB3DF</t>
         </is>
@@ -22035,7 +22685,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22100,6 +22750,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-CB81C0D23F74</t>
         </is>
@@ -22136,7 +22796,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22201,6 +22861,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-428460E90510</t>
         </is>
@@ -22237,7 +22907,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22302,6 +22972,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-C5DBDBD2DFB2</t>
         </is>
@@ -22338,7 +23018,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22403,6 +23083,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-CFB037DF4922</t>
         </is>
@@ -22439,7 +23129,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22504,6 +23194,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-7F9DFC4C2BE9</t>
         </is>
@@ -22540,7 +23240,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22605,6 +23305,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-EDA0CCAEDF49</t>
         </is>
@@ -22641,7 +23351,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22706,6 +23416,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-999707D7730E</t>
         </is>
@@ -22742,7 +23462,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22807,6 +23527,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-52E2C6F052EB</t>
         </is>
@@ -22843,7 +23573,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22908,6 +23638,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-372DC5670ECB</t>
         </is>
@@ -22944,7 +23684,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23009,6 +23749,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-F6461F86A451</t>
         </is>
@@ -23045,7 +23795,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23110,6 +23860,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-FD060B0E337A</t>
         </is>
@@ -23146,7 +23906,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23211,6 +23971,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-19D3A74A1659</t>
         </is>
@@ -23247,7 +24017,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23312,6 +24082,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-AC58D04CE1F3</t>
         </is>

--- a/product_upload/packages/12/file.xlsx
+++ b/product_upload/packages/12/file.xlsx
@@ -1279,8 +1279,16 @@
           <t>3261116787-391-121987161294</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STELAZINE 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>STELAZINE 5MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1466,8 +1474,16 @@
           <t>7216359630-054-734411598009</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STELAZINE 1MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>STELAZINE 1MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1653,8 +1669,16 @@
           <t>8214998591-782-240370146570</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STERILE WATER FOR INJ 500 ML</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>STERILE WATER FOR INJ 500 ML detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1838,8 +1862,16 @@
           <t>1858670698-984-906651828612</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STERILE WATER FOR IRRIG.IN ACCUMED PS.CT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>STERILE WATER FOR IRRIG.IN ACCUMED PS.CT detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2023,8 +2055,16 @@
           <t>9605999685-150-401964318792</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STERILE WATER FOR IRRIG.IN ACCUMED PS.CT</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>STERILE WATER FOR IRRIG.IN ACCUMED PS.CT detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2208,8 +2248,16 @@
           <t>4258047914-010-697122112212</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STERILE WATER FOR IRRIG.IN ACCUMED PS.CT</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>STERILE WATER FOR IRRIG.IN ACCUMED PS.CT detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2397,8 +2445,16 @@
           <t>1434584614-807-321954940537</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STIEPROX 1.5% SHAMPOO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>STIEPROX 1.5% SHAMPOO detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2588,8 +2644,16 @@
           <t>6361489234-793-078501706160</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STERILE WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>STERILE WATER FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2777,8 +2841,16 @@
           <t>8512603153-847-729009417031</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STERILE WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>STERILE WATER FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2966,8 +3038,16 @@
           <t>7898485266-245-883699435441</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STERILE WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>STERILE WATER FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3159,8 +3239,16 @@
           <t>5556673766-385-590322245618</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STERILE WATER FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>STERILE WATER FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3348,8 +3436,16 @@
           <t>8089787130-093-540348630896</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SMOFKABIVEN PERIPHERAL EMULSION for infusion</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SMOFKABIVEN PERIPHERAL EMULSION for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3939,8 +4035,16 @@
           <t>9163662438-231-623484829101</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SIMVAGEN 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SIMVAGEN 40 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4130,8 +4234,16 @@
           <t>5075043586-911-023562771400</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SIMVAGEN 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>SIMVAGEN 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4321,8 +4433,16 @@
           <t>4811838147-744-660679933351</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SIMVAGEN 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SIMVAGEN 10 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4906,8 +5026,16 @@
           <t>2274352789-608-239777052570</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SMOFKABIVEN PERIPHERAL EMULSION for infusion</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SMOFKABIVEN PERIPHERAL EMULSION for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5101,8 +5229,16 @@
           <t>2199063506-355-785882886698</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SMOFKABIVEN PERIPHERAL EMULSION for infusion</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>SMOFKABIVEN PERIPHERAL EMULSION for infusion detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5300,8 +5436,16 @@
           <t>9131749220-107-627280766327</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SNAFI 20MG TAB</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SNAFI 20MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5682,8 +5826,16 @@
           <t>4788781543-923-831903228046</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOD. CHLORIDE 0.45%+DEXTROSE 5% I.V INF.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SOD. CHLORIDE 0.45%+DEXTROSE 5% I.V INF. detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5873,8 +6025,16 @@
           <t>9782627597-119-998016797719</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SIMCOR 20 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SIMCOR 20 MG F-C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6064,8 +6224,16 @@
           <t>2428834107-894-345615295793</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SILVER NITRATE EYE DROP</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SILVER NITRATE EYE DROP detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6438,8 +6606,16 @@
           <t>9367013383-604-152832004931</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEROQUEL 25 MG TAB</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SEROQUEL 25 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -7023,8 +7199,16 @@
           <t>6555745700-572-776894811495</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SERMION TAB 5MG</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SERMION TAB 5MG detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7214,8 +7398,16 @@
           <t>3912747298-497-713923507792</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SERMION 10MG TAB</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SERMION 10MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -8573,8 +8765,16 @@
           <t>5809314512-460-159164024731</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEROQUEL XL 200MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>SEROQUEL XL 200MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -10137,8 +10337,16 @@
           <t>3833007647-066-140881424315</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SIMCOR 10 MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>SIMCOR 10 MG F-C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -11910,8 +12118,16 @@
           <t>0592455779-466-855458361229</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SODIUM CHLORIDE .9% + DEXTROSE 5%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>SODIUM CHLORIDE .9% + DEXTROSE 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12101,8 +12317,16 @@
           <t>6083785375-248-180598258698</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SODIUM CHLORIDE 0.9% &amp; GLUCOSE 5% I.V</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>SODIUM CHLORIDE 0.9% &amp; GLUCOSE 5% I.V detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12296,8 +12520,16 @@
           <t>9005892475-036-087895130118</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SODIUM CHLORIDE 0.45% AND GLUCOSE 5% I.V</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>SODIUM CHLORIDE 0.45% AND GLUCOSE 5% I.V detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12487,8 +12719,16 @@
           <t>7563502639-823-023655637904</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SODIUM CHLORIDE 0.225&amp;+DEXTROSE5%I.V INF</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>SODIUM CHLORIDE 0.225&amp;+DEXTROSE5%I.V INF detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12686,8 +12926,16 @@
           <t>0707986515-961-750148659949</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SODIUM ACETATE F.T.V.40mEq</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>SODIUM ACETATE F.T.V.40mEq detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12877,8 +13125,16 @@
           <t>8886109968-584-215275435334</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOD.CHLORIDE 0.9% FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>SOD.CHLORIDE 0.9% FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13068,8 +13324,16 @@
           <t>3002957548-534-491492990563</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOD.CHLORIDE 0.9% FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>SOD.CHLORIDE 0.9% FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13263,8 +13527,16 @@
           <t>4626118012-768-818925665046</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOD.CHLORIDE 0.9% FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>SOD.CHLORIDE 0.9% FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13454,8 +13726,16 @@
           <t>5054081099-534-708354233967</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOD.CHLORIDE 0.9% FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>SOD.CHLORIDE 0.9% FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13641,8 +13921,16 @@
           <t>5774134012-206-188996829231</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOD.CHLORIDE 0.9% FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>SOD.CHLORIDE 0.9% FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13832,8 +14120,16 @@
           <t>8805466804-284-382991655980</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ 0.9% w/v SODIUM CHLORIDE for irrigation</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0.9% w/v SODIUM CHLORIDE for irrigation detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14019,8 +14315,16 @@
           <t>3073888449-947-502479810934</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOD.CHLORIDE 0.9% FOR IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>SOD.CHLORIDE 0.9% FOR IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14210,8 +14514,16 @@
           <t>3929826669-303-382751662432</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LACTATED RINGERS INJECTION USP 500 ML</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>LACTATED RINGERS INJECTION USP 500 ML detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -15002,8 +15314,16 @@
           <t>6456283320-512-925736297819</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLAVODAR 457MG/5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>CLAVODAR 457MG/5ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15384,8 +15704,16 @@
           <t>0321649176-775-693820268020</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARIXIN 500 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>CLARIXIN 500 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15579,8 +15907,16 @@
           <t>0953578302-890-110751169824</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARIVA 250 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>CLARIVA 250 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15770,8 +16106,16 @@
           <t>4956908800-571-925492446148</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARITT XL 500MG EXTENDED RELEASE TABLETS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>CLARITT XL 500MG EXTENDED RELEASE TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16156,8 +16500,16 @@
           <t>2484539778-438-869777728258</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLINIMYCIN-T</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>CLINIMYCIN-T detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16343,8 +16695,16 @@
           <t>7275501399-598-974573407802</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLINIMYCIN-T</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>CLINIMYCIN-T detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16534,8 +16894,16 @@
           <t>8555230031-693-102678495851</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLIOCORT</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>CLIOCORT detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16725,8 +17093,16 @@
           <t>9675761943-657-193188970418</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOPIXOL TABS 25MG</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>CLOPIXOL TABS 25MG detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16916,8 +17292,16 @@
           <t>4267443058-671-325421186139</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOPIXOL TABS 10MG</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>CLOPIXOL TABS 10MG detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17107,8 +17491,16 @@
           <t>8569456253-046-531977304777</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARITT XL 500 MG EXTENDED RELEASE TAB.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>CLARITT XL 500 MG EXTENDED RELEASE TAB. detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17294,8 +17686,16 @@
           <t>6525174243-523-372064108188</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOFAST 1% GEL</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>CLOFAST 1% GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17867,8 +18267,16 @@
           <t>6515160597-347-705706459979</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOBESON</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>CLOBESON detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18058,8 +18466,16 @@
           <t>5342057649-175-439239255572</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLOBEDERM</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>CLOBEDERM detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18241,8 +18657,16 @@
           <t>3811409738-711-470655983655</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLORACEF 250MG/5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>CLORACEF 250MG/5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18627,8 +19051,16 @@
           <t>9627533203-194-842108071685</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARITT 250 MG - 5 ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>CLARITT 250 MG - 5 ML SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18814,8 +19246,16 @@
           <t>7058080633-340-500018641685</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CITANEST 3% DENTAL OCTAPRESSIN CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>CITANEST 3% DENTAL OCTAPRESSIN CARTRIDGE detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19005,8 +19445,16 @@
           <t>8891376354-556-646155393034</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CITALOPRAM HEXAL 40MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>CITALOPRAM HEXAL 40MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19200,8 +19648,16 @@
           <t>7111928938-532-045449797191</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CITALOPRAM HEXAL 20MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>CITALOPRAM HEXAL 20MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19391,8 +19847,16 @@
           <t>5335696013-201-946994657954</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CITALOGEN 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>CITALOGEN 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19777,8 +20241,16 @@
           <t>6833287482-669-108943475111</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CITRIN 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>CITRIN 5MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/12/file.xlsx
+++ b/product_upload/packages/12/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22229,7 +22229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22310,40 +22310,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22423,38 +22428,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>209.15</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-BEAE6FDB35E0</t>
         </is>
@@ -22534,38 +22544,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>142.59</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-F4E9C3C5015C</t>
         </is>
@@ -22645,38 +22660,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>141.49</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-10F31E1B83B8</t>
         </is>
@@ -22756,38 +22776,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>336.07</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-3456071ACD86</t>
         </is>
@@ -22867,38 +22892,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>181.98</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-58AE8919296C</t>
         </is>
@@ -22978,38 +23008,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>428.08</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-30257D494980</t>
         </is>
@@ -23089,38 +23124,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>29.6</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-7A81459AB3DF</t>
         </is>
@@ -23200,38 +23240,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>74.62</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-CB81C0D23F74</t>
         </is>
@@ -23311,38 +23356,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>368</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-428460E90510</t>
         </is>
@@ -23422,38 +23472,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>215.27</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-C5DBDBD2DFB2</t>
         </is>
@@ -23533,38 +23588,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>247.54</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-CFB037DF4922</t>
         </is>
@@ -23644,38 +23704,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>185.07</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-7F9DFC4C2BE9</t>
         </is>
@@ -23755,38 +23820,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>303.53</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-EDA0CCAEDF49</t>
         </is>
@@ -23866,38 +23936,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>82.98999999999999</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-999707D7730E</t>
         </is>
@@ -23977,38 +24052,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>472.51</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-52E2C6F052EB</t>
         </is>
@@ -24088,38 +24168,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>284.69</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-372DC5670ECB</t>
         </is>
@@ -24199,38 +24284,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>457.65</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-F6461F86A451</t>
         </is>
@@ -24310,38 +24400,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>377.79</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-FD060B0E337A</t>
         </is>
@@ -24421,38 +24516,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>168.25</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-19D3A74A1659</t>
         </is>
@@ -24532,38 +24632,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>452.11</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-AC58D04CE1F3</t>
         </is>
